--- a/outputs/Airborne_Particle_Test_Result_and_Graph.xlsx
+++ b/outputs/Airborne_Particle_Test_Result_and_Graph.xlsx
@@ -261,12 +261,36 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'AHU-33 0.5'!$C$2:$C$19</f>
+              <f>'AHU-33 0.5'!$L$2:$L$22</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'AHU-33 0.5'!$D$2:$D$19</f>
+              <f>'AHU-33 0.5'!$D$2:$D$22</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'AHU-33 0.5'!E1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'AHU-33 0.5'!$L$2:$L$22</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'AHU-33 0.5'!$E$2:$E$22</f>
             </numRef>
           </val>
         </ser>
@@ -277,11 +301,11 @@
       <lineChart>
         <grouping val="standard"/>
         <ser>
-          <idx val="1"/>
-          <order val="1"/>
+          <idx val="2"/>
+          <order val="2"/>
           <tx>
             <strRef>
-              <f>'AHU-33 0.5'!E1</f>
+              <f>'AHU-33 0.5'!F1</f>
             </strRef>
           </tx>
           <spPr>
@@ -302,17 +326,17 @@
           </marker>
           <val>
             <numRef>
-              <f>'AHU-33 0.5'!$E$2:$E$19</f>
+              <f>'AHU-33 0.5'!$F$2:$F$22</f>
             </numRef>
           </val>
           <smooth val="0"/>
         </ser>
         <ser>
-          <idx val="2"/>
-          <order val="2"/>
+          <idx val="3"/>
+          <order val="3"/>
           <tx>
             <strRef>
-              <f>'AHU-33 0.5'!F1</f>
+              <f>'AHU-33 0.5'!G1</f>
             </strRef>
           </tx>
           <spPr>
@@ -333,17 +357,17 @@
           </marker>
           <val>
             <numRef>
-              <f>'AHU-33 0.5'!$F$2:$F$19</f>
+              <f>'AHU-33 0.5'!$G$2:$G$22</f>
             </numRef>
           </val>
           <smooth val="0"/>
         </ser>
         <ser>
-          <idx val="3"/>
-          <order val="3"/>
+          <idx val="4"/>
+          <order val="4"/>
           <tx>
             <strRef>
-              <f>'AHU-33 0.5'!G1</f>
+              <f>'AHU-33 0.5'!H1</f>
             </strRef>
           </tx>
           <spPr>
@@ -364,17 +388,17 @@
           </marker>
           <val>
             <numRef>
-              <f>'AHU-33 0.5'!$G$2:$G$19</f>
+              <f>'AHU-33 0.5'!$H$2:$H$22</f>
             </numRef>
           </val>
           <smooth val="0"/>
         </ser>
         <ser>
-          <idx val="4"/>
-          <order val="4"/>
+          <idx val="5"/>
+          <order val="5"/>
           <tx>
             <strRef>
-              <f>'AHU-33 0.5'!H1</f>
+              <f>'AHU-33 0.5'!I1</f>
             </strRef>
           </tx>
           <spPr>
@@ -395,17 +419,17 @@
           </marker>
           <val>
             <numRef>
-              <f>'AHU-33 0.5'!$H$2:$H$19</f>
+              <f>'AHU-33 0.5'!$I$2:$I$22</f>
             </numRef>
           </val>
           <smooth val="0"/>
         </ser>
         <ser>
-          <idx val="5"/>
-          <order val="5"/>
+          <idx val="6"/>
+          <order val="6"/>
           <tx>
             <strRef>
-              <f>'AHU-33 0.5'!I1</f>
+              <f>'AHU-33 0.5'!J1</f>
             </strRef>
           </tx>
           <spPr>
@@ -426,17 +450,17 @@
           </marker>
           <val>
             <numRef>
-              <f>'AHU-33 0.5'!$I$2:$I$19</f>
+              <f>'AHU-33 0.5'!$J$2:$J$22</f>
             </numRef>
           </val>
           <smooth val="0"/>
         </ser>
         <ser>
-          <idx val="6"/>
-          <order val="6"/>
+          <idx val="7"/>
+          <order val="7"/>
           <tx>
             <strRef>
-              <f>'AHU-33 0.5'!J1</f>
+              <f>'AHU-33 0.5'!K1</f>
             </strRef>
           </tx>
           <spPr>
@@ -457,7 +481,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'AHU-33 0.5'!$J$2:$J$19</f>
+              <f>'AHU-33 0.5'!$K$2:$K$22</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -503,22 +527,6 @@
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
-        <majorGridlines/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>측정값</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
@@ -571,12 +579,36 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'AHU-33 5.0'!$C$2:$C$19</f>
+              <f>'AHU-33 5.0'!$M$2:$M$22</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'AHU-33 5.0'!$D$2:$D$19</f>
+              <f>'AHU-33 5.0'!$D$2:$D$22</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'AHU-33 5.0'!E1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'AHU-33 5.0'!$M$2:$M$22</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'AHU-33 5.0'!$E$2:$E$22</f>
             </numRef>
           </val>
         </ser>
@@ -587,11 +619,11 @@
       <lineChart>
         <grouping val="standard"/>
         <ser>
-          <idx val="1"/>
-          <order val="1"/>
+          <idx val="2"/>
+          <order val="2"/>
           <tx>
             <strRef>
-              <f>'AHU-33 5.0'!E1</f>
+              <f>'AHU-33 5.0'!F1</f>
             </strRef>
           </tx>
           <spPr>
@@ -612,17 +644,17 @@
           </marker>
           <val>
             <numRef>
-              <f>'AHU-33 5.0'!$E$2:$E$19</f>
+              <f>'AHU-33 5.0'!$F$2:$F$22</f>
             </numRef>
           </val>
           <smooth val="0"/>
         </ser>
         <ser>
-          <idx val="2"/>
-          <order val="2"/>
+          <idx val="3"/>
+          <order val="3"/>
           <tx>
             <strRef>
-              <f>'AHU-33 5.0'!F1</f>
+              <f>'AHU-33 5.0'!G1</f>
             </strRef>
           </tx>
           <spPr>
@@ -643,17 +675,17 @@
           </marker>
           <val>
             <numRef>
-              <f>'AHU-33 5.0'!$F$2:$F$19</f>
+              <f>'AHU-33 5.0'!$G$2:$G$22</f>
             </numRef>
           </val>
           <smooth val="0"/>
         </ser>
         <ser>
-          <idx val="3"/>
-          <order val="3"/>
+          <idx val="4"/>
+          <order val="4"/>
           <tx>
             <strRef>
-              <f>'AHU-33 5.0'!G1</f>
+              <f>'AHU-33 5.0'!H1</f>
             </strRef>
           </tx>
           <spPr>
@@ -674,17 +706,17 @@
           </marker>
           <val>
             <numRef>
-              <f>'AHU-33 5.0'!$G$2:$G$19</f>
+              <f>'AHU-33 5.0'!$H$2:$H$22</f>
             </numRef>
           </val>
           <smooth val="0"/>
         </ser>
         <ser>
-          <idx val="4"/>
-          <order val="4"/>
+          <idx val="5"/>
+          <order val="5"/>
           <tx>
             <strRef>
-              <f>'AHU-33 5.0'!H1</f>
+              <f>'AHU-33 5.0'!I1</f>
             </strRef>
           </tx>
           <spPr>
@@ -705,17 +737,17 @@
           </marker>
           <val>
             <numRef>
-              <f>'AHU-33 5.0'!$H$2:$H$19</f>
+              <f>'AHU-33 5.0'!$I$2:$I$22</f>
             </numRef>
           </val>
           <smooth val="0"/>
         </ser>
         <ser>
-          <idx val="5"/>
-          <order val="5"/>
+          <idx val="6"/>
+          <order val="6"/>
           <tx>
             <strRef>
-              <f>'AHU-33 5.0'!I1</f>
+              <f>'AHU-33 5.0'!J1</f>
             </strRef>
           </tx>
           <spPr>
@@ -736,17 +768,17 @@
           </marker>
           <val>
             <numRef>
-              <f>'AHU-33 5.0'!$I$2:$I$19</f>
+              <f>'AHU-33 5.0'!$J$2:$J$22</f>
             </numRef>
           </val>
           <smooth val="0"/>
         </ser>
         <ser>
-          <idx val="6"/>
-          <order val="6"/>
+          <idx val="7"/>
+          <order val="7"/>
           <tx>
             <strRef>
-              <f>'AHU-33 5.0'!J1</f>
+              <f>'AHU-33 5.0'!K1</f>
             </strRef>
           </tx>
           <spPr>
@@ -767,17 +799,17 @@
           </marker>
           <val>
             <numRef>
-              <f>'AHU-33 5.0'!$J$2:$J$19</f>
+              <f>'AHU-33 5.0'!$K$2:$K$22</f>
             </numRef>
           </val>
           <smooth val="0"/>
         </ser>
         <ser>
-          <idx val="7"/>
-          <order val="7"/>
+          <idx val="8"/>
+          <order val="8"/>
           <tx>
             <strRef>
-              <f>'AHU-33 5.0'!K1</f>
+              <f>'AHU-33 5.0'!L1</f>
             </strRef>
           </tx>
           <spPr>
@@ -798,7 +830,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'AHU-33 5.0'!$K$2:$K$19</f>
+              <f>'AHU-33 5.0'!$L$2:$L$22</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -844,22 +876,6 @@
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
-        <majorGridlines/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>측정값</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
@@ -879,12 +895,12 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>11</col>
+      <col>12</col>
       <colOff>0</colOff>
       <row>0</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="12960000" cy="6480000"/>
+    <ext cx="24192000" cy="8640000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -906,12 +922,12 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>12</col>
+      <col>13</col>
       <colOff>0</colOff>
       <row>0</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="12960000" cy="6480000"/>
+    <ext cx="24192000" cy="8640000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -1218,7 +1234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J55"/>
+  <dimension ref="A1:J102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1329,14 +1345,14 @@
         <v>1</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G9" s="6">
         <f>AVERAGE(F9:F14)</f>
         <v/>
       </c>
       <c r="H9" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I9" s="6">
         <f>AVERAGE(H9:H14)</f>
@@ -1344,7 +1360,7 @@
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>2025 (하)</t>
+          <t>2026 (상)</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1434,12 @@
       <c r="E13" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="F13" s="6" t="n">
-        <v>107</v>
+      <c r="F13" s="8" t="n">
+        <v>800</v>
       </c>
       <c r="G13" s="7" t="n"/>
       <c r="H13" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13" s="7" t="n"/>
       <c r="J13" s="7" t="n"/>
@@ -1484,7 +1500,7 @@
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>2025 (하)</t>
+          <t>2026 (상)</t>
         </is>
       </c>
     </row>
@@ -1499,7 +1515,7 @@
         <v>2</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>570</v>
+        <v>990</v>
       </c>
       <c r="G16" s="7" t="n"/>
       <c r="H16" s="6" t="n">
@@ -1624,7 +1640,7 @@
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>2025 (하)</t>
+          <t>2026 (상)</t>
         </is>
       </c>
     </row>
@@ -1684,7 +1700,7 @@
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>2025 (하)</t>
+          <t>2026 (상)</t>
         </is>
       </c>
     </row>
@@ -1764,7 +1780,7 @@
       </c>
       <c r="J26" s="6" t="inlineStr">
         <is>
-          <t>2025 (하)</t>
+          <t>2026 (상)</t>
         </is>
       </c>
     </row>
@@ -1804,7 +1820,7 @@
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>2025 (하)</t>
+          <t>2026 (상)</t>
         </is>
       </c>
     </row>
@@ -1864,7 +1880,7 @@
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
-          <t>2025 (하)</t>
+          <t>2026 (상)</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1940,7 @@
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
-          <t>2025 (하)</t>
+          <t>2026 (상)</t>
         </is>
       </c>
     </row>
@@ -1984,7 +2000,7 @@
       </c>
       <c r="J33" s="6" t="inlineStr">
         <is>
-          <t>2025 (하)</t>
+          <t>2026 (상)</t>
         </is>
       </c>
     </row>
@@ -2044,7 +2060,7 @@
       </c>
       <c r="J35" s="6" t="inlineStr">
         <is>
-          <t>2025 (하)</t>
+          <t>2026 (상)</t>
         </is>
       </c>
     </row>
@@ -2104,7 +2120,7 @@
       </c>
       <c r="J37" s="6" t="inlineStr">
         <is>
-          <t>2025 (하)</t>
+          <t>2026 (상)</t>
         </is>
       </c>
     </row>
@@ -2164,7 +2180,7 @@
       </c>
       <c r="J39" s="6" t="inlineStr">
         <is>
-          <t>2025 (하)</t>
+          <t>2026 (상)</t>
         </is>
       </c>
     </row>
@@ -2304,7 +2320,7 @@
       </c>
       <c r="J45" s="6" t="inlineStr">
         <is>
-          <t>2025 (하)</t>
+          <t>2026 (상)</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2380,7 @@
       </c>
       <c r="J47" s="6" t="inlineStr">
         <is>
-          <t>2025 (하)</t>
+          <t>2026 (상)</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2440,7 @@
       </c>
       <c r="J49" s="6" t="inlineStr">
         <is>
-          <t>2025 (하)</t>
+          <t>2026 (상)</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2478,7 @@
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>퇴실</t>
+          <t>튜실</t>
         </is>
       </c>
       <c r="E51" s="6" t="n">
@@ -2484,7 +2500,7 @@
       </c>
       <c r="J51" s="6" t="inlineStr">
         <is>
-          <t>2025 (하)</t>
+          <t>2026 (상)</t>
         </is>
       </c>
     </row>
@@ -2524,7 +2540,7 @@
       </c>
       <c r="J52" s="6" t="inlineStr">
         <is>
-          <t>2025 (하)</t>
+          <t>2026 (상)</t>
         </is>
       </c>
     </row>
@@ -2584,7 +2600,7 @@
       </c>
       <c r="J54" s="6" t="inlineStr">
         <is>
-          <t>2025 (하)</t>
+          <t>2026 (상)</t>
         </is>
       </c>
     </row>
@@ -2608,98 +2624,1483 @@
       <c r="I55" s="5" t="n"/>
       <c r="J55" s="5" t="n"/>
     </row>
+    <row r="56">
+      <c r="A56" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="n">
+        <v>2142</v>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t>무균 실험실</t>
+        </is>
+      </c>
+      <c r="E56" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F56" s="6" t="n">
+        <v>121</v>
+      </c>
+      <c r="G56" s="6">
+        <f>AVERAGE(F56:F61)</f>
+        <v/>
+      </c>
+      <c r="H56" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="I56" s="6">
+        <f>AVERAGE(H56:H61)</f>
+        <v/>
+      </c>
+      <c r="J56" s="6" t="inlineStr">
+        <is>
+          <t>2025 (하)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="n">
+        <v>49</v>
+      </c>
+      <c r="B57" s="7" t="n"/>
+      <c r="C57" s="7" t="n"/>
+      <c r="D57" s="7" t="n"/>
+      <c r="E57" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F57" s="6" t="n">
+        <v>194</v>
+      </c>
+      <c r="G57" s="7" t="n"/>
+      <c r="H57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" s="7" t="n"/>
+      <c r="J57" s="7" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="B58" s="7" t="n"/>
+      <c r="C58" s="7" t="n"/>
+      <c r="D58" s="7" t="n"/>
+      <c r="E58" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F58" s="8" t="n">
+        <v>676</v>
+      </c>
+      <c r="G58" s="7" t="n"/>
+      <c r="H58" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="I58" s="7" t="n"/>
+      <c r="J58" s="7" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="B59" s="7" t="n"/>
+      <c r="C59" s="7" t="n"/>
+      <c r="D59" s="7" t="n"/>
+      <c r="E59" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F59" s="6" t="n">
+        <v>576</v>
+      </c>
+      <c r="G59" s="7" t="n"/>
+      <c r="H59" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="I59" s="7" t="n"/>
+      <c r="J59" s="7" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="n">
+        <v>52</v>
+      </c>
+      <c r="B60" s="7" t="n"/>
+      <c r="C60" s="7" t="n"/>
+      <c r="D60" s="7" t="n"/>
+      <c r="E60" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="F60" s="6" t="n">
+        <v>107</v>
+      </c>
+      <c r="G60" s="7" t="n"/>
+      <c r="H60" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I60" s="7" t="n"/>
+      <c r="J60" s="7" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="n">
+        <v>53</v>
+      </c>
+      <c r="B61" s="5" t="n"/>
+      <c r="C61" s="5" t="n"/>
+      <c r="D61" s="5" t="n"/>
+      <c r="E61" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="F61" s="6" t="n">
+        <v>121</v>
+      </c>
+      <c r="G61" s="5" t="n"/>
+      <c r="H61" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I61" s="5" t="n"/>
+      <c r="J61" s="5" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="n">
+        <v>54</v>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="n">
+        <v>2165</v>
+      </c>
+      <c r="D62" s="6" t="inlineStr">
+        <is>
+          <t>균주집중실</t>
+        </is>
+      </c>
+      <c r="E62" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F62" s="6" t="n">
+        <v>5420</v>
+      </c>
+      <c r="G62" s="6">
+        <f>AVERAGE(F62:F67)</f>
+        <v/>
+      </c>
+      <c r="H62" s="6" t="n">
+        <v>400</v>
+      </c>
+      <c r="I62" s="6">
+        <f>AVERAGE(H62:H67)</f>
+        <v/>
+      </c>
+      <c r="J62" s="6" t="inlineStr">
+        <is>
+          <t>2025 (하)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="n">
+        <v>55</v>
+      </c>
+      <c r="B63" s="7" t="n"/>
+      <c r="C63" s="7" t="n"/>
+      <c r="D63" s="7" t="n"/>
+      <c r="E63" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F63" s="6" t="n">
+        <v>570</v>
+      </c>
+      <c r="G63" s="7" t="n"/>
+      <c r="H63" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="I63" s="7" t="n"/>
+      <c r="J63" s="7" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="n">
+        <v>56</v>
+      </c>
+      <c r="B64" s="7" t="n"/>
+      <c r="C64" s="7" t="n"/>
+      <c r="D64" s="7" t="n"/>
+      <c r="E64" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F64" s="6" t="n">
+        <v>660</v>
+      </c>
+      <c r="G64" s="7" t="n"/>
+      <c r="H64" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="I64" s="7" t="n"/>
+      <c r="J64" s="7" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="n">
+        <v>57</v>
+      </c>
+      <c r="B65" s="7" t="n"/>
+      <c r="C65" s="7" t="n"/>
+      <c r="D65" s="7" t="n"/>
+      <c r="E65" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F65" s="6" t="n">
+        <v>4000</v>
+      </c>
+      <c r="G65" s="7" t="n"/>
+      <c r="H65" s="6" t="n">
+        <v>620</v>
+      </c>
+      <c r="I65" s="7" t="n"/>
+      <c r="J65" s="7" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="n">
+        <v>58</v>
+      </c>
+      <c r="B66" s="7" t="n"/>
+      <c r="C66" s="7" t="n"/>
+      <c r="D66" s="7" t="n"/>
+      <c r="E66" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="F66" s="6" t="n">
+        <v>690</v>
+      </c>
+      <c r="G66" s="7" t="n"/>
+      <c r="H66" s="6" t="n">
+        <v>110</v>
+      </c>
+      <c r="I66" s="7" t="n"/>
+      <c r="J66" s="7" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="n">
+        <v>59</v>
+      </c>
+      <c r="B67" s="5" t="n"/>
+      <c r="C67" s="5" t="n"/>
+      <c r="D67" s="5" t="n"/>
+      <c r="E67" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="F67" s="6" t="n">
+        <v>600</v>
+      </c>
+      <c r="G67" s="5" t="n"/>
+      <c r="H67" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="I67" s="5" t="n"/>
+      <c r="J67" s="5" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="n">
+        <v>2147</v>
+      </c>
+      <c r="D68" s="6" t="inlineStr">
+        <is>
+          <t>탈의실</t>
+        </is>
+      </c>
+      <c r="E68" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F68" s="8" t="n">
+        <v>30760</v>
+      </c>
+      <c r="G68" s="6">
+        <f>AVERAGE(F68:F69)</f>
+        <v/>
+      </c>
+      <c r="H68" s="6" t="n">
+        <v>1340</v>
+      </c>
+      <c r="I68" s="6">
+        <f>AVERAGE(H68:H69)</f>
+        <v/>
+      </c>
+      <c r="J68" s="6" t="inlineStr">
+        <is>
+          <t>2025 (하)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="6" t="n">
+        <v>61</v>
+      </c>
+      <c r="B69" s="5" t="n"/>
+      <c r="C69" s="5" t="n"/>
+      <c r="D69" s="5" t="n"/>
+      <c r="E69" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F69" s="6" t="n">
+        <v>17690</v>
+      </c>
+      <c r="G69" s="5" t="n"/>
+      <c r="H69" s="6" t="n">
+        <v>550</v>
+      </c>
+      <c r="I69" s="5" t="n"/>
+      <c r="J69" s="5" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="6" t="n">
+        <v>62</v>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="n">
+        <v>2169</v>
+      </c>
+      <c r="D70" s="6" t="inlineStr">
+        <is>
+          <t>복도</t>
+        </is>
+      </c>
+      <c r="E70" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F70" s="6" t="n">
+        <v>11140</v>
+      </c>
+      <c r="G70" s="6">
+        <f>AVERAGE(F70:F72)</f>
+        <v/>
+      </c>
+      <c r="H70" s="6" t="n">
+        <v>1670</v>
+      </c>
+      <c r="I70" s="6">
+        <f>AVERAGE(H70:H72)</f>
+        <v/>
+      </c>
+      <c r="J70" s="6" t="inlineStr">
+        <is>
+          <t>2025 (하)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="6" t="n">
+        <v>63</v>
+      </c>
+      <c r="B71" s="7" t="n"/>
+      <c r="C71" s="7" t="n"/>
+      <c r="D71" s="7" t="n"/>
+      <c r="E71" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F71" s="6" t="n">
+        <v>4120</v>
+      </c>
+      <c r="G71" s="7" t="n"/>
+      <c r="H71" s="6" t="n">
+        <v>650</v>
+      </c>
+      <c r="I71" s="7" t="n"/>
+      <c r="J71" s="7" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="6" t="n">
+        <v>64</v>
+      </c>
+      <c r="B72" s="5" t="n"/>
+      <c r="C72" s="5" t="n"/>
+      <c r="D72" s="5" t="n"/>
+      <c r="E72" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F72" s="6" t="n">
+        <v>4710</v>
+      </c>
+      <c r="G72" s="5" t="n"/>
+      <c r="H72" s="6" t="n">
+        <v>590</v>
+      </c>
+      <c r="I72" s="5" t="n"/>
+      <c r="J72" s="5" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="B73" s="6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="n">
+        <v>2145</v>
+      </c>
+      <c r="D73" s="6" t="inlineStr">
+        <is>
+          <t>탈의실</t>
+        </is>
+      </c>
+      <c r="E73" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F73" s="6" t="n">
+        <v>54260</v>
+      </c>
+      <c r="G73" s="6">
+        <f>AVERAGE(F73:F73)</f>
+        <v/>
+      </c>
+      <c r="H73" s="6" t="n">
+        <v>1170</v>
+      </c>
+      <c r="I73" s="6">
+        <f>AVERAGE(H73:H73)</f>
+        <v/>
+      </c>
+      <c r="J73" s="6" t="inlineStr">
+        <is>
+          <t>2025 (하)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="6" t="n">
+        <v>66</v>
+      </c>
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="n">
+        <v>2142</v>
+      </c>
+      <c r="D74" s="6" t="inlineStr">
+        <is>
+          <t>PASS BOX(QHA-745)</t>
+        </is>
+      </c>
+      <c r="E74" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F74" s="6" t="n">
+        <v>539</v>
+      </c>
+      <c r="G74" s="6">
+        <f>AVERAGE(F74:F75)</f>
+        <v/>
+      </c>
+      <c r="H74" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I74" s="6">
+        <f>AVERAGE(H74:H75)</f>
+        <v/>
+      </c>
+      <c r="J74" s="6" t="inlineStr">
+        <is>
+          <t>2025 (하)</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="6" t="n">
+        <v>67</v>
+      </c>
+      <c r="B75" s="5" t="n"/>
+      <c r="C75" s="5" t="n"/>
+      <c r="D75" s="5" t="n"/>
+      <c r="E75" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F75" s="6" t="n">
+        <v>317</v>
+      </c>
+      <c r="G75" s="5" t="n"/>
+      <c r="H75" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I75" s="5" t="n"/>
+      <c r="J75" s="5" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="n">
+        <v>2142</v>
+      </c>
+      <c r="D76" s="6" t="inlineStr">
+        <is>
+          <t>PASS BOX(QHA-744)</t>
+        </is>
+      </c>
+      <c r="E76" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F76" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="G76" s="6">
+        <f>AVERAGE(F76:F77)</f>
+        <v/>
+      </c>
+      <c r="H76" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I76" s="6">
+        <f>AVERAGE(H76:H77)</f>
+        <v/>
+      </c>
+      <c r="J76" s="6" t="inlineStr">
+        <is>
+          <t>2025 (하)</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="6" t="n">
+        <v>69</v>
+      </c>
+      <c r="B77" s="5" t="n"/>
+      <c r="C77" s="5" t="n"/>
+      <c r="D77" s="5" t="n"/>
+      <c r="E77" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F77" s="6" t="n">
+        <v>114</v>
+      </c>
+      <c r="G77" s="5" t="n"/>
+      <c r="H77" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I77" s="5" t="n"/>
+      <c r="J77" s="5" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="n">
+        <v>70</v>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="n">
+        <v>2169</v>
+      </c>
+      <c r="D78" s="6" t="inlineStr">
+        <is>
+          <t>PASS BOX(QHA-743)</t>
+        </is>
+      </c>
+      <c r="E78" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F78" s="6" t="n">
+        <v>25830</v>
+      </c>
+      <c r="G78" s="6">
+        <f>AVERAGE(F78:F79)</f>
+        <v/>
+      </c>
+      <c r="H78" s="6" t="n">
+        <v>2240</v>
+      </c>
+      <c r="I78" s="6">
+        <f>AVERAGE(H78:H79)</f>
+        <v/>
+      </c>
+      <c r="J78" s="6" t="inlineStr">
+        <is>
+          <t>2025 (하)</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="6" t="n">
+        <v>71</v>
+      </c>
+      <c r="B79" s="5" t="n"/>
+      <c r="C79" s="5" t="n"/>
+      <c r="D79" s="5" t="n"/>
+      <c r="E79" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F79" s="6" t="n">
+        <v>30810</v>
+      </c>
+      <c r="G79" s="5" t="n"/>
+      <c r="H79" s="6" t="n">
+        <v>2960</v>
+      </c>
+      <c r="I79" s="5" t="n"/>
+      <c r="J79" s="5" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="6" t="n">
+        <v>72</v>
+      </c>
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="n">
+        <v>2169</v>
+      </c>
+      <c r="D80" s="6" t="inlineStr">
+        <is>
+          <t>PASS BOX(QHA-742)</t>
+        </is>
+      </c>
+      <c r="E80" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F80" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="G80" s="6">
+        <f>AVERAGE(F80:F81)</f>
+        <v/>
+      </c>
+      <c r="H80" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I80" s="6">
+        <f>AVERAGE(H80:H81)</f>
+        <v/>
+      </c>
+      <c r="J80" s="6" t="inlineStr">
+        <is>
+          <t>2025 (하)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="6" t="n">
+        <v>73</v>
+      </c>
+      <c r="B81" s="5" t="n"/>
+      <c r="C81" s="5" t="n"/>
+      <c r="D81" s="5" t="n"/>
+      <c r="E81" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F81" s="6" t="n">
+        <v>70</v>
+      </c>
+      <c r="G81" s="5" t="n"/>
+      <c r="H81" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I81" s="5" t="n"/>
+      <c r="J81" s="5" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="6" t="n">
+        <v>74</v>
+      </c>
+      <c r="B82" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C82" s="6" t="n">
+        <v>2142</v>
+      </c>
+      <c r="D82" s="6" t="inlineStr">
+        <is>
+          <t>무균시험실 BSC</t>
+        </is>
+      </c>
+      <c r="E82" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F82" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="G82" s="6">
+        <f>AVERAGE(F82:F83)</f>
+        <v/>
+      </c>
+      <c r="H82" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" s="6">
+        <f>AVERAGE(H82:H83)</f>
+        <v/>
+      </c>
+      <c r="J82" s="6" t="inlineStr">
+        <is>
+          <t>2025 (하)</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="6" t="n">
+        <v>75</v>
+      </c>
+      <c r="B83" s="5" t="n"/>
+      <c r="C83" s="5" t="n"/>
+      <c r="D83" s="5" t="n"/>
+      <c r="E83" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F83" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G83" s="5" t="n"/>
+      <c r="H83" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" s="5" t="n"/>
+      <c r="J83" s="5" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="6" t="n">
+        <v>76</v>
+      </c>
+      <c r="B84" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C84" s="6" t="n">
+        <v>2165</v>
+      </c>
+      <c r="D84" s="6" t="inlineStr">
+        <is>
+          <t>균주집중실 BSC</t>
+        </is>
+      </c>
+      <c r="E84" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F84" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="G84" s="6">
+        <f>AVERAGE(F84:F85)</f>
+        <v/>
+      </c>
+      <c r="H84" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I84" s="6">
+        <f>AVERAGE(H84:H85)</f>
+        <v/>
+      </c>
+      <c r="J84" s="6" t="inlineStr">
+        <is>
+          <t>2025 (하)</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="6" t="n">
+        <v>77</v>
+      </c>
+      <c r="B85" s="5" t="n"/>
+      <c r="C85" s="5" t="n"/>
+      <c r="D85" s="5" t="n"/>
+      <c r="E85" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F85" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" s="5" t="n"/>
+      <c r="H85" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" s="5" t="n"/>
+      <c r="J85" s="5" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="6" t="n">
+        <v>78</v>
+      </c>
+      <c r="B86" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C86" s="6" t="n">
+        <v>2144</v>
+      </c>
+      <c r="D86" s="6" t="inlineStr">
+        <is>
+          <t>미생물 시험실</t>
+        </is>
+      </c>
+      <c r="E86" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F86" s="6" t="n">
+        <v>6360</v>
+      </c>
+      <c r="G86" s="6">
+        <f>AVERAGE(F86:F91)</f>
+        <v/>
+      </c>
+      <c r="H86" s="6" t="n">
+        <v>410</v>
+      </c>
+      <c r="I86" s="6">
+        <f>AVERAGE(H86:H91)</f>
+        <v/>
+      </c>
+      <c r="J86" s="6" t="inlineStr">
+        <is>
+          <t>2025 (하)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="6" t="n">
+        <v>79</v>
+      </c>
+      <c r="B87" s="7" t="n"/>
+      <c r="C87" s="7" t="n"/>
+      <c r="D87" s="7" t="n"/>
+      <c r="E87" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F87" s="6" t="n">
+        <v>3730</v>
+      </c>
+      <c r="G87" s="7" t="n"/>
+      <c r="H87" s="6" t="n">
+        <v>410</v>
+      </c>
+      <c r="I87" s="7" t="n"/>
+      <c r="J87" s="7" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="B88" s="7" t="n"/>
+      <c r="C88" s="7" t="n"/>
+      <c r="D88" s="7" t="n"/>
+      <c r="E88" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F88" s="6" t="n">
+        <v>5110</v>
+      </c>
+      <c r="G88" s="7" t="n"/>
+      <c r="H88" s="6" t="n">
+        <v>560</v>
+      </c>
+      <c r="I88" s="7" t="n"/>
+      <c r="J88" s="7" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="6" t="n">
+        <v>81</v>
+      </c>
+      <c r="B89" s="7" t="n"/>
+      <c r="C89" s="7" t="n"/>
+      <c r="D89" s="7" t="n"/>
+      <c r="E89" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F89" s="6" t="n">
+        <v>4140</v>
+      </c>
+      <c r="G89" s="7" t="n"/>
+      <c r="H89" s="6" t="n">
+        <v>390</v>
+      </c>
+      <c r="I89" s="7" t="n"/>
+      <c r="J89" s="7" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="6" t="n">
+        <v>82</v>
+      </c>
+      <c r="B90" s="7" t="n"/>
+      <c r="C90" s="7" t="n"/>
+      <c r="D90" s="7" t="n"/>
+      <c r="E90" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="F90" s="6" t="n">
+        <v>1520</v>
+      </c>
+      <c r="G90" s="7" t="n"/>
+      <c r="H90" s="6" t="n">
+        <v>140</v>
+      </c>
+      <c r="I90" s="7" t="n"/>
+      <c r="J90" s="7" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="6" t="n">
+        <v>83</v>
+      </c>
+      <c r="B91" s="5" t="n"/>
+      <c r="C91" s="5" t="n"/>
+      <c r="D91" s="5" t="n"/>
+      <c r="E91" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="F91" s="6" t="n">
+        <v>4620</v>
+      </c>
+      <c r="G91" s="5" t="n"/>
+      <c r="H91" s="6" t="n">
+        <v>600</v>
+      </c>
+      <c r="I91" s="5" t="n"/>
+      <c r="J91" s="5" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="6" t="n">
+        <v>84</v>
+      </c>
+      <c r="B92" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C92" s="6" t="n">
+        <v>2144</v>
+      </c>
+      <c r="D92" s="6" t="inlineStr">
+        <is>
+          <t>미생물 시험실 C/B(852)</t>
+        </is>
+      </c>
+      <c r="E92" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F92" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G92" s="6">
+        <f>AVERAGE(F92:F93)</f>
+        <v/>
+      </c>
+      <c r="H92" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" s="6">
+        <f>AVERAGE(H92:H93)</f>
+        <v/>
+      </c>
+      <c r="J92" s="6" t="inlineStr">
+        <is>
+          <t>2025 (하)</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="6" t="n">
+        <v>85</v>
+      </c>
+      <c r="B93" s="5" t="n"/>
+      <c r="C93" s="5" t="n"/>
+      <c r="D93" s="5" t="n"/>
+      <c r="E93" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F93" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G93" s="5" t="n"/>
+      <c r="H93" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I93" s="5" t="n"/>
+      <c r="J93" s="5" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="6" t="n">
+        <v>86</v>
+      </c>
+      <c r="B94" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C94" s="6" t="n">
+        <v>2144</v>
+      </c>
+      <c r="D94" s="6" t="inlineStr">
+        <is>
+          <t>미생물 시험실 C/B(853)</t>
+        </is>
+      </c>
+      <c r="E94" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F94" s="6" t="n">
+        <v>116</v>
+      </c>
+      <c r="G94" s="6">
+        <f>AVERAGE(F94:F95)</f>
+        <v/>
+      </c>
+      <c r="H94" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I94" s="6">
+        <f>AVERAGE(H94:H95)</f>
+        <v/>
+      </c>
+      <c r="J94" s="6" t="inlineStr">
+        <is>
+          <t>2025 (하)</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="6" t="n">
+        <v>87</v>
+      </c>
+      <c r="B95" s="5" t="n"/>
+      <c r="C95" s="5" t="n"/>
+      <c r="D95" s="5" t="n"/>
+      <c r="E95" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F95" s="6" t="n">
+        <v>101</v>
+      </c>
+      <c r="G95" s="5" t="n"/>
+      <c r="H95" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I95" s="5" t="n"/>
+      <c r="J95" s="5" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="6" t="n">
+        <v>88</v>
+      </c>
+      <c r="B96" s="6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C96" s="6" t="n">
+        <v>2146</v>
+      </c>
+      <c r="D96" s="6" t="inlineStr">
+        <is>
+          <t>착의실</t>
+        </is>
+      </c>
+      <c r="E96" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F96" s="6" t="n">
+        <v>14580</v>
+      </c>
+      <c r="G96" s="6">
+        <f>AVERAGE(F96:F97)</f>
+        <v/>
+      </c>
+      <c r="H96" s="6" t="n">
+        <v>1340</v>
+      </c>
+      <c r="I96" s="6">
+        <f>AVERAGE(H96:H97)</f>
+        <v/>
+      </c>
+      <c r="J96" s="6" t="inlineStr">
+        <is>
+          <t>2025 (하)</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="6" t="n">
+        <v>89</v>
+      </c>
+      <c r="B97" s="5" t="n"/>
+      <c r="C97" s="5" t="n"/>
+      <c r="D97" s="5" t="n"/>
+      <c r="E97" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F97" s="6" t="n">
+        <v>106930</v>
+      </c>
+      <c r="G97" s="5" t="n"/>
+      <c r="H97" s="8" t="n">
+        <v>14230</v>
+      </c>
+      <c r="I97" s="5" t="n"/>
+      <c r="J97" s="5" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="B98" s="6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C98" s="6" t="n">
+        <v>2150</v>
+      </c>
+      <c r="D98" s="6" t="inlineStr">
+        <is>
+          <t>퇴실</t>
+        </is>
+      </c>
+      <c r="E98" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F98" s="6" t="n">
+        <v>5070</v>
+      </c>
+      <c r="G98" s="6">
+        <f>AVERAGE(F98:F98)</f>
+        <v/>
+      </c>
+      <c r="H98" s="6" t="n">
+        <v>230</v>
+      </c>
+      <c r="I98" s="6">
+        <f>AVERAGE(H98:H98)</f>
+        <v/>
+      </c>
+      <c r="J98" s="6" t="inlineStr">
+        <is>
+          <t>2025 (하)</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="6" t="n">
+        <v>91</v>
+      </c>
+      <c r="B99" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C99" s="6" t="n">
+        <v>2148</v>
+      </c>
+      <c r="D99" s="6" t="inlineStr">
+        <is>
+          <t>착의실</t>
+        </is>
+      </c>
+      <c r="E99" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F99" s="6" t="n">
+        <v>18110</v>
+      </c>
+      <c r="G99" s="6">
+        <f>AVERAGE(F99:F100)</f>
+        <v/>
+      </c>
+      <c r="H99" s="6" t="n">
+        <v>1010</v>
+      </c>
+      <c r="I99" s="6">
+        <f>AVERAGE(H99:H100)</f>
+        <v/>
+      </c>
+      <c r="J99" s="6" t="inlineStr">
+        <is>
+          <t>2025 (하)</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="6" t="n">
+        <v>92</v>
+      </c>
+      <c r="B100" s="5" t="n"/>
+      <c r="C100" s="5" t="n"/>
+      <c r="D100" s="5" t="n"/>
+      <c r="E100" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F100" s="6" t="n">
+        <v>2460</v>
+      </c>
+      <c r="G100" s="5" t="n"/>
+      <c r="H100" s="6" t="n">
+        <v>110</v>
+      </c>
+      <c r="I100" s="5" t="n"/>
+      <c r="J100" s="5" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="6" t="n">
+        <v>93</v>
+      </c>
+      <c r="B101" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C101" s="6" t="n">
+        <v>2149</v>
+      </c>
+      <c r="D101" s="6" t="inlineStr">
+        <is>
+          <t>착의실</t>
+        </is>
+      </c>
+      <c r="E101" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F101" s="6" t="n">
+        <v>416</v>
+      </c>
+      <c r="G101" s="6">
+        <f>AVERAGE(F101:F102)</f>
+        <v/>
+      </c>
+      <c r="H101" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I101" s="6">
+        <f>AVERAGE(H101:H102)</f>
+        <v/>
+      </c>
+      <c r="J101" s="6" t="inlineStr">
+        <is>
+          <t>2025 (하)</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="6" t="n">
+        <v>94</v>
+      </c>
+      <c r="B102" s="5" t="n"/>
+      <c r="C102" s="5" t="n"/>
+      <c r="D102" s="5" t="n"/>
+      <c r="E102" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F102" s="6" t="n">
+        <v>331</v>
+      </c>
+      <c r="G102" s="5" t="n"/>
+      <c r="H102" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I102" s="5" t="n"/>
+      <c r="J102" s="5" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="104">
+  <mergeCells count="200">
     <mergeCell ref="I54:I55"/>
+    <mergeCell ref="J82:J83"/>
     <mergeCell ref="B52:B53"/>
+    <mergeCell ref="D99:D100"/>
     <mergeCell ref="C29:C30"/>
     <mergeCell ref="D52:D53"/>
     <mergeCell ref="I15:I20"/>
     <mergeCell ref="A7:A8"/>
     <mergeCell ref="D21:D22"/>
+    <mergeCell ref="G82:G83"/>
+    <mergeCell ref="G86:G91"/>
+    <mergeCell ref="I86:I91"/>
+    <mergeCell ref="C94:C95"/>
     <mergeCell ref="C23:C25"/>
+    <mergeCell ref="B101:B102"/>
     <mergeCell ref="B29:B30"/>
     <mergeCell ref="D45:D46"/>
+    <mergeCell ref="D101:D102"/>
+    <mergeCell ref="J68:J69"/>
+    <mergeCell ref="G74:G75"/>
     <mergeCell ref="D7:D8"/>
+    <mergeCell ref="B78:B79"/>
     <mergeCell ref="D47:D48"/>
+    <mergeCell ref="G68:G69"/>
+    <mergeCell ref="D78:D79"/>
+    <mergeCell ref="I68:I69"/>
     <mergeCell ref="J45:J46"/>
     <mergeCell ref="G49:G50"/>
     <mergeCell ref="B37:B38"/>
+    <mergeCell ref="G62:G67"/>
+    <mergeCell ref="I62:I67"/>
+    <mergeCell ref="I56:I61"/>
+    <mergeCell ref="G76:G77"/>
+    <mergeCell ref="B80:B81"/>
     <mergeCell ref="G33:G34"/>
+    <mergeCell ref="C56:C61"/>
+    <mergeCell ref="J94:J95"/>
     <mergeCell ref="J47:J48"/>
+    <mergeCell ref="J86:J91"/>
     <mergeCell ref="C27:C28"/>
+    <mergeCell ref="I82:I83"/>
     <mergeCell ref="I29:I30"/>
     <mergeCell ref="J31:J32"/>
     <mergeCell ref="G35:G36"/>
     <mergeCell ref="B54:B55"/>
     <mergeCell ref="I35:I36"/>
     <mergeCell ref="D54:D55"/>
+    <mergeCell ref="B70:B72"/>
+    <mergeCell ref="G84:G85"/>
+    <mergeCell ref="J76:J77"/>
     <mergeCell ref="B23:B25"/>
+    <mergeCell ref="D70:D72"/>
+    <mergeCell ref="I84:I85"/>
     <mergeCell ref="I31:I32"/>
+    <mergeCell ref="G99:G100"/>
     <mergeCell ref="D15:D20"/>
+    <mergeCell ref="I99:I100"/>
     <mergeCell ref="G21:G22"/>
+    <mergeCell ref="J62:J67"/>
     <mergeCell ref="B35:B36"/>
+    <mergeCell ref="J70:J72"/>
     <mergeCell ref="G9:G14"/>
+    <mergeCell ref="G101:G102"/>
     <mergeCell ref="I9:I14"/>
     <mergeCell ref="B27:B28"/>
     <mergeCell ref="I45:I46"/>
     <mergeCell ref="D27:D28"/>
     <mergeCell ref="D49:D50"/>
+    <mergeCell ref="I101:I102"/>
+    <mergeCell ref="C86:C91"/>
+    <mergeCell ref="J74:J75"/>
     <mergeCell ref="C45:C46"/>
+    <mergeCell ref="G78:G79"/>
     <mergeCell ref="C54:C55"/>
     <mergeCell ref="I23:I25"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="J27:J28"/>
     <mergeCell ref="G39:G44"/>
     <mergeCell ref="C47:C48"/>
+    <mergeCell ref="J99:J100"/>
     <mergeCell ref="C31:C32"/>
     <mergeCell ref="I33:I34"/>
     <mergeCell ref="J35:J36"/>
+    <mergeCell ref="C76:C77"/>
+    <mergeCell ref="B84:B85"/>
+    <mergeCell ref="I96:I97"/>
+    <mergeCell ref="J101:J102"/>
+    <mergeCell ref="G70:G72"/>
+    <mergeCell ref="I70:I72"/>
+    <mergeCell ref="C82:C83"/>
     <mergeCell ref="G15:G20"/>
     <mergeCell ref="D37:D38"/>
     <mergeCell ref="J21:J22"/>
+    <mergeCell ref="B92:B93"/>
     <mergeCell ref="B45:B46"/>
     <mergeCell ref="D9:D14"/>
     <mergeCell ref="G27:G28"/>
     <mergeCell ref="D39:D44"/>
+    <mergeCell ref="C74:C75"/>
+    <mergeCell ref="C68:C69"/>
     <mergeCell ref="B7:B8"/>
+    <mergeCell ref="B94:B95"/>
+    <mergeCell ref="D94:D95"/>
     <mergeCell ref="C49:C50"/>
+    <mergeCell ref="J92:J93"/>
+    <mergeCell ref="C101:C102"/>
     <mergeCell ref="B31:B32"/>
     <mergeCell ref="G52:G53"/>
     <mergeCell ref="J39:J44"/>
+    <mergeCell ref="D80:D81"/>
+    <mergeCell ref="B82:B83"/>
+    <mergeCell ref="D76:D77"/>
+    <mergeCell ref="C84:C85"/>
+    <mergeCell ref="B62:B67"/>
+    <mergeCell ref="C80:C81"/>
+    <mergeCell ref="B56:B61"/>
     <mergeCell ref="I47:I48"/>
     <mergeCell ref="C21:C22"/>
     <mergeCell ref="J15:J20"/>
     <mergeCell ref="G37:G38"/>
     <mergeCell ref="I37:I38"/>
+    <mergeCell ref="G80:G81"/>
+    <mergeCell ref="B68:B69"/>
     <mergeCell ref="C9:C14"/>
+    <mergeCell ref="D68:D69"/>
+    <mergeCell ref="G92:G93"/>
     <mergeCell ref="B49:B50"/>
     <mergeCell ref="F7:I7"/>
+    <mergeCell ref="D56:D61"/>
+    <mergeCell ref="D92:D93"/>
     <mergeCell ref="C7:C8"/>
     <mergeCell ref="B33:B34"/>
     <mergeCell ref="I39:I44"/>
     <mergeCell ref="E7:E8"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="G94:G95"/>
+    <mergeCell ref="B99:B100"/>
+    <mergeCell ref="I94:I95"/>
     <mergeCell ref="G23:G25"/>
     <mergeCell ref="D29:D30"/>
     <mergeCell ref="C39:C44"/>
     <mergeCell ref="J52:J53"/>
     <mergeCell ref="B9:B14"/>
+    <mergeCell ref="J56:J61"/>
     <mergeCell ref="J33:J34"/>
+    <mergeCell ref="I74:I75"/>
     <mergeCell ref="D31:D32"/>
     <mergeCell ref="J29:J30"/>
+    <mergeCell ref="I80:I81"/>
     <mergeCell ref="I49:I50"/>
     <mergeCell ref="B21:B22"/>
     <mergeCell ref="I27:I28"/>
+    <mergeCell ref="C62:C67"/>
+    <mergeCell ref="I76:I77"/>
+    <mergeCell ref="C70:C72"/>
     <mergeCell ref="B47:B48"/>
+    <mergeCell ref="J84:J85"/>
+    <mergeCell ref="J78:J79"/>
+    <mergeCell ref="B96:B97"/>
+    <mergeCell ref="G56:G61"/>
     <mergeCell ref="C33:C34"/>
+    <mergeCell ref="D96:D97"/>
     <mergeCell ref="C15:C20"/>
     <mergeCell ref="J37:J38"/>
     <mergeCell ref="C35:C36"/>
     <mergeCell ref="D23:D25"/>
     <mergeCell ref="J9:J14"/>
+    <mergeCell ref="B86:B91"/>
     <mergeCell ref="B39:B44"/>
+    <mergeCell ref="D86:D91"/>
     <mergeCell ref="I52:I53"/>
     <mergeCell ref="I21:I22"/>
+    <mergeCell ref="C99:C100"/>
+    <mergeCell ref="I92:I93"/>
+    <mergeCell ref="J80:J81"/>
     <mergeCell ref="J54:J55"/>
     <mergeCell ref="J7:J8"/>
     <mergeCell ref="J23:J25"/>
@@ -2707,13 +4108,24 @@
     <mergeCell ref="C52:C53"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="D33:D34"/>
+    <mergeCell ref="B74:B75"/>
+    <mergeCell ref="D74:D75"/>
+    <mergeCell ref="I78:I79"/>
     <mergeCell ref="G45:G46"/>
+    <mergeCell ref="C96:C97"/>
     <mergeCell ref="B15:B20"/>
     <mergeCell ref="G54:G55"/>
+    <mergeCell ref="D62:D67"/>
+    <mergeCell ref="B76:B77"/>
+    <mergeCell ref="J96:J97"/>
     <mergeCell ref="G47:G48"/>
+    <mergeCell ref="D82:D83"/>
+    <mergeCell ref="G96:G97"/>
     <mergeCell ref="C37:C38"/>
     <mergeCell ref="G31:G32"/>
     <mergeCell ref="D35:D36"/>
+    <mergeCell ref="D84:D85"/>
+    <mergeCell ref="C92:C93"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2725,7 +4137,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2792,14 +4204,14 @@
         </is>
       </c>
       <c r="E2" s="6" t="n">
-        <v>299</v>
+        <v>414</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>5</v>
+        <v>4.666666666666667</v>
       </c>
       <c r="G2" s="6" t="inlineStr">
         <is>
-          <t>2025 (하)</t>
+          <t>2026 (상)</t>
         </is>
       </c>
     </row>
@@ -2821,14 +4233,14 @@
         </is>
       </c>
       <c r="E3" s="6" t="n">
-        <v>1990</v>
+        <v>2060</v>
       </c>
       <c r="F3" s="6" t="n">
         <v>201.6666666666667</v>
       </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>2025 (하)</t>
+          <t>2026 (상)</t>
         </is>
       </c>
     </row>
@@ -2857,7 +4269,7 @@
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>2025 (하)</t>
+          <t>2026 (상)</t>
         </is>
       </c>
     </row>
@@ -2886,7 +4298,7 @@
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>2025 (하)</t>
+          <t>2026 (상)</t>
         </is>
       </c>
     </row>
@@ -2915,7 +4327,7 @@
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>2025 (하)</t>
+          <t>2026 (상)</t>
         </is>
       </c>
     </row>
@@ -2944,7 +4356,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2025 (하)</t>
+          <t>2026 (상)</t>
         </is>
       </c>
     </row>
@@ -2973,7 +4385,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2025 (하)</t>
+          <t>2026 (상)</t>
         </is>
       </c>
     </row>
@@ -3002,7 +4414,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2025 (하)</t>
+          <t>2026 (상)</t>
         </is>
       </c>
     </row>
@@ -3031,7 +4443,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2025 (하)</t>
+          <t>2026 (상)</t>
         </is>
       </c>
     </row>
@@ -3060,7 +4472,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2025 (하)</t>
+          <t>2026 (상)</t>
         </is>
       </c>
     </row>
@@ -3089,7 +4501,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2025 (하)</t>
+          <t>2026 (상)</t>
         </is>
       </c>
     </row>
@@ -3118,7 +4530,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2025 (하)</t>
+          <t>2026 (상)</t>
         </is>
       </c>
     </row>
@@ -3147,7 +4559,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2025 (하)</t>
+          <t>2026 (상)</t>
         </is>
       </c>
     </row>
@@ -3176,7 +4588,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2025 (하)</t>
+          <t>2026 (상)</t>
         </is>
       </c>
     </row>
@@ -3205,7 +4617,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>2025 (하)</t>
+          <t>2026 (상)</t>
         </is>
       </c>
     </row>
@@ -3223,7 +4635,7 @@
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>퇴실</t>
+          <t>튜실</t>
         </is>
       </c>
       <c r="E17" s="6" t="n">
@@ -3234,7 +4646,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2025 (하)</t>
+          <t>2026 (상)</t>
         </is>
       </c>
     </row>
@@ -3263,7 +4675,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2025 (하)</t>
+          <t>2026 (상)</t>
         </is>
       </c>
     </row>
@@ -3291,6 +4703,528 @@
         <v>4</v>
       </c>
       <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>2026 (상)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>2142</v>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>무균 실험실</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>299</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>2025 (하)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>2165</v>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>균주집중실</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>1990</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>201.6666666666667</v>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>2025 (하)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>2147</v>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>탈의실</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>24225</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>945</v>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>2025 (하)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>2169</v>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>복도</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>6657</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>970</v>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>2025 (하)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="n">
+        <v>2145</v>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>탈의실</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="n">
+        <v>54260</v>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>1170</v>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>2025 (하)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>2142</v>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>PASS BOX(QHA-745)</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>428</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>2025 (하)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>2142</v>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>PASS BOX(QHA-744)</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>102</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>2025 (하)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>2169</v>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>PASS BOX(QHA-743)</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>28320</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>2600</v>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>2025 (하)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>2169</v>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>PASS BOX(QHA-742)</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="F28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>2025 (하)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="n">
+        <v>2142</v>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>무균시험실 BSC</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>2025 (하)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="n">
+        <v>2165</v>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>균주집중실 BSC</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F30" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>2025 (하)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="n">
+        <v>2144</v>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>미생물 시험실</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>4247</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>418.3333333333333</v>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>2025 (하)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="n">
+        <v>2144</v>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>미생물 시험실 C/B(852)</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>2025 (하)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="n">
+        <v>2144</v>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>미생물 시험실 C/B(853)</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>108</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>2025 (하)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="n">
+        <v>2146</v>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>착의실</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="n">
+        <v>60755</v>
+      </c>
+      <c r="F34" s="6" t="n">
+        <v>7785</v>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>2025 (하)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="n">
+        <v>2150</v>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>퇴실</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="n">
+        <v>5070</v>
+      </c>
+      <c r="F35" s="6" t="n">
+        <v>230</v>
+      </c>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>2025 (하)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="n">
+        <v>2148</v>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>착의실</t>
+        </is>
+      </c>
+      <c r="E36" s="6" t="n">
+        <v>10285</v>
+      </c>
+      <c r="F36" s="6" t="n">
+        <v>560</v>
+      </c>
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>2025 (하)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="n">
+        <v>2149</v>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>착의실</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="n">
+        <v>374</v>
+      </c>
+      <c r="F37" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="G37" s="6" t="inlineStr">
         <is>
           <t>2025 (하)</t>
         </is>
@@ -3307,745 +5241,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>청정등급</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>실번호</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>실명</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>2025 (하)</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Grade A 경고기준: 23</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Grade A 조치기준: 46</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Grade B 경고기준: 627</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Grade B 조치기준: 3,254</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Grade C 경고기준: 23,402</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Grade C 조치기준: 46,804</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2142</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>무균 실험실</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>299</v>
-      </c>
-      <c r="E2" t="n">
-        <v>23</v>
-      </c>
-      <c r="F2" t="n">
-        <v>46</v>
-      </c>
-      <c r="G2" t="n">
-        <v>627</v>
-      </c>
-      <c r="H2" t="n">
-        <v>3254</v>
-      </c>
-      <c r="I2" t="n">
-        <v>23402</v>
-      </c>
-      <c r="J2" t="n">
-        <v>46804</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>2165</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>균주접종실</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>1990</v>
-      </c>
-      <c r="E3" t="n">
-        <v>23</v>
-      </c>
-      <c r="F3" t="n">
-        <v>46</v>
-      </c>
-      <c r="G3" t="n">
-        <v>627</v>
-      </c>
-      <c r="H3" t="n">
-        <v>3254</v>
-      </c>
-      <c r="I3" t="n">
-        <v>23402</v>
-      </c>
-      <c r="J3" t="n">
-        <v>46804</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>2147</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>탈의실</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>24225</v>
-      </c>
-      <c r="E4" t="n">
-        <v>23</v>
-      </c>
-      <c r="F4" t="n">
-        <v>46</v>
-      </c>
-      <c r="G4" t="n">
-        <v>627</v>
-      </c>
-      <c r="H4" t="n">
-        <v>3254</v>
-      </c>
-      <c r="I4" t="n">
-        <v>23402</v>
-      </c>
-      <c r="J4" t="n">
-        <v>46804</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>2169</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>복도</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>6657</v>
-      </c>
-      <c r="E5" t="n">
-        <v>23</v>
-      </c>
-      <c r="F5" t="n">
-        <v>46</v>
-      </c>
-      <c r="G5" t="n">
-        <v>627</v>
-      </c>
-      <c r="H5" t="n">
-        <v>3254</v>
-      </c>
-      <c r="I5" t="n">
-        <v>23402</v>
-      </c>
-      <c r="J5" t="n">
-        <v>46804</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>2145</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>탈의실</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>54260</v>
-      </c>
-      <c r="E6" t="n">
-        <v>23</v>
-      </c>
-      <c r="F6" t="n">
-        <v>46</v>
-      </c>
-      <c r="G6" t="n">
-        <v>627</v>
-      </c>
-      <c r="H6" t="n">
-        <v>3254</v>
-      </c>
-      <c r="I6" t="n">
-        <v>23402</v>
-      </c>
-      <c r="J6" t="n">
-        <v>46804</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>2142</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>PASS BOX(QHA-745)</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>428</v>
-      </c>
-      <c r="E7" t="n">
-        <v>23</v>
-      </c>
-      <c r="F7" t="n">
-        <v>46</v>
-      </c>
-      <c r="G7" t="n">
-        <v>627</v>
-      </c>
-      <c r="H7" t="n">
-        <v>3254</v>
-      </c>
-      <c r="I7" t="n">
-        <v>23402</v>
-      </c>
-      <c r="J7" t="n">
-        <v>46804</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>2142</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>PASS BOX(QHA-744)</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>102</v>
-      </c>
-      <c r="E8" t="n">
-        <v>23</v>
-      </c>
-      <c r="F8" t="n">
-        <v>46</v>
-      </c>
-      <c r="G8" t="n">
-        <v>627</v>
-      </c>
-      <c r="H8" t="n">
-        <v>3254</v>
-      </c>
-      <c r="I8" t="n">
-        <v>23402</v>
-      </c>
-      <c r="J8" t="n">
-        <v>46804</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>2169</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>PASS BOX(QHA-743)</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>28320</v>
-      </c>
-      <c r="E9" t="n">
-        <v>23</v>
-      </c>
-      <c r="F9" t="n">
-        <v>46</v>
-      </c>
-      <c r="G9" t="n">
-        <v>627</v>
-      </c>
-      <c r="H9" t="n">
-        <v>3254</v>
-      </c>
-      <c r="I9" t="n">
-        <v>23402</v>
-      </c>
-      <c r="J9" t="n">
-        <v>46804</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>2169</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>PASS BOX(QHA-742)</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>65</v>
-      </c>
-      <c r="E10" t="n">
-        <v>23</v>
-      </c>
-      <c r="F10" t="n">
-        <v>46</v>
-      </c>
-      <c r="G10" t="n">
-        <v>627</v>
-      </c>
-      <c r="H10" t="n">
-        <v>3254</v>
-      </c>
-      <c r="I10" t="n">
-        <v>23402</v>
-      </c>
-      <c r="J10" t="n">
-        <v>46804</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>2142</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>무균시험실 BSC</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>2</v>
-      </c>
-      <c r="E11" t="n">
-        <v>23</v>
-      </c>
-      <c r="F11" t="n">
-        <v>46</v>
-      </c>
-      <c r="G11" t="n">
-        <v>627</v>
-      </c>
-      <c r="H11" t="n">
-        <v>3254</v>
-      </c>
-      <c r="I11" t="n">
-        <v>23402</v>
-      </c>
-      <c r="J11" t="n">
-        <v>46804</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>2165</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>균주접종실 BSC</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>2</v>
-      </c>
-      <c r="E12" t="n">
-        <v>23</v>
-      </c>
-      <c r="F12" t="n">
-        <v>46</v>
-      </c>
-      <c r="G12" t="n">
-        <v>627</v>
-      </c>
-      <c r="H12" t="n">
-        <v>3254</v>
-      </c>
-      <c r="I12" t="n">
-        <v>23402</v>
-      </c>
-      <c r="J12" t="n">
-        <v>46804</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>2144</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>미생물 시험실</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>4247</v>
-      </c>
-      <c r="E13" t="n">
-        <v>23</v>
-      </c>
-      <c r="F13" t="n">
-        <v>46</v>
-      </c>
-      <c r="G13" t="n">
-        <v>627</v>
-      </c>
-      <c r="H13" t="n">
-        <v>3254</v>
-      </c>
-      <c r="I13" t="n">
-        <v>23402</v>
-      </c>
-      <c r="J13" t="n">
-        <v>46804</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>2144</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>미생물 시험실 C/B(852)</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>23</v>
-      </c>
-      <c r="F14" t="n">
-        <v>46</v>
-      </c>
-      <c r="G14" t="n">
-        <v>627</v>
-      </c>
-      <c r="H14" t="n">
-        <v>3254</v>
-      </c>
-      <c r="I14" t="n">
-        <v>23402</v>
-      </c>
-      <c r="J14" t="n">
-        <v>46804</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>2144</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>미생물 시험실 C/B(853)</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>108</v>
-      </c>
-      <c r="E15" t="n">
-        <v>23</v>
-      </c>
-      <c r="F15" t="n">
-        <v>46</v>
-      </c>
-      <c r="G15" t="n">
-        <v>627</v>
-      </c>
-      <c r="H15" t="n">
-        <v>3254</v>
-      </c>
-      <c r="I15" t="n">
-        <v>23402</v>
-      </c>
-      <c r="J15" t="n">
-        <v>46804</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>2146</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>착의실</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>60755</v>
-      </c>
-      <c r="E16" t="n">
-        <v>23</v>
-      </c>
-      <c r="F16" t="n">
-        <v>46</v>
-      </c>
-      <c r="G16" t="n">
-        <v>627</v>
-      </c>
-      <c r="H16" t="n">
-        <v>3254</v>
-      </c>
-      <c r="I16" t="n">
-        <v>23402</v>
-      </c>
-      <c r="J16" t="n">
-        <v>46804</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>2150</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>퇴실</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>5070</v>
-      </c>
-      <c r="E17" t="n">
-        <v>23</v>
-      </c>
-      <c r="F17" t="n">
-        <v>46</v>
-      </c>
-      <c r="G17" t="n">
-        <v>627</v>
-      </c>
-      <c r="H17" t="n">
-        <v>3254</v>
-      </c>
-      <c r="I17" t="n">
-        <v>23402</v>
-      </c>
-      <c r="J17" t="n">
-        <v>46804</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>2148</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>착의실</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>10285</v>
-      </c>
-      <c r="E18" t="n">
-        <v>23</v>
-      </c>
-      <c r="F18" t="n">
-        <v>46</v>
-      </c>
-      <c r="G18" t="n">
-        <v>627</v>
-      </c>
-      <c r="H18" t="n">
-        <v>3254</v>
-      </c>
-      <c r="I18" t="n">
-        <v>23402</v>
-      </c>
-      <c r="J18" t="n">
-        <v>46804</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>2149</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>착의실</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>374</v>
-      </c>
-      <c r="E19" t="n">
-        <v>23</v>
-      </c>
-      <c r="F19" t="n">
-        <v>46</v>
-      </c>
-      <c r="G19" t="n">
-        <v>627</v>
-      </c>
-      <c r="H19" t="n">
-        <v>3254</v>
-      </c>
-      <c r="I19" t="n">
-        <v>23402</v>
-      </c>
-      <c r="J19" t="n">
-        <v>46804</v>
-      </c>
-    </row>
-    <row r="21" ht="45" customHeight="1">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>참고: 위 차트에서 특정 등급의 제한선이 표시되지 않는 경우, 해당 등급의 모든 측정 결과가 아직 기준을 만족하고 있음을 의미합니다. 해당 등급의 제한선은 제한값이 매우 높아 차트 표시 범위를 초과하므로 나타나지 않습니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22"/>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A21:D22"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:L25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4059,6 +5255,7 @@
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="28" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4079,42 +5276,47 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>2026 (상)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>2025 (하)</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Grade A 경고기준: 4</t>
-        </is>
-      </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Grade A 조치기준: 8</t>
+          <t>Grade A 경고기준: 23</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Grade B 경고기준: 13</t>
+          <t>Grade A 조치기준: 46</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Grade B 조치기준: 26</t>
+          <t>Grade B 경고기준: 627</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Grade C 경고기준: 1,540</t>
+          <t>Grade B 조치기준: 3,254</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>Grade C 조치기준: 2,900</t>
+          <t>Grade C 경고기준: 23,402</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Grade D 경고기준: 8,183</t>
+          <t>Grade C 조치기준: 46,804</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>표시명</t>
         </is>
       </c>
     </row>
@@ -4133,28 +5335,35 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>414</v>
       </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>299</v>
       </c>
       <c r="F2" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="G2" t="n">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="H2" t="n">
-        <v>26</v>
+        <v>627</v>
       </c>
       <c r="I2" t="n">
-        <v>1540</v>
+        <v>3254</v>
       </c>
       <c r="J2" t="n">
-        <v>2900</v>
+        <v>23402</v>
       </c>
       <c r="K2" t="n">
-        <v>8183</v>
+        <v>46804</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>B
+무균 실험실
+2142</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -4172,28 +5381,32 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>201.6666666666667</v>
-      </c>
-      <c r="E3" t="n">
-        <v>4</v>
+        <v>2060</v>
       </c>
       <c r="F3" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="G3" t="n">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="H3" t="n">
-        <v>26</v>
+        <v>627</v>
       </c>
       <c r="I3" t="n">
-        <v>1540</v>
+        <v>3254</v>
       </c>
       <c r="J3" t="n">
-        <v>2900</v>
+        <v>23402</v>
       </c>
       <c r="K3" t="n">
-        <v>8183</v>
+        <v>46804</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>D
+균주접종실
+2165</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -4211,28 +5424,35 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>945</v>
+        <v>24225</v>
       </c>
       <c r="E4" t="n">
-        <v>4</v>
+        <v>24225</v>
       </c>
       <c r="F4" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="G4" t="n">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="H4" t="n">
-        <v>26</v>
+        <v>627</v>
       </c>
       <c r="I4" t="n">
-        <v>1540</v>
+        <v>3254</v>
       </c>
       <c r="J4" t="n">
-        <v>2900</v>
+        <v>23402</v>
       </c>
       <c r="K4" t="n">
-        <v>8183</v>
+        <v>46804</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>C
+탈의실
+2147</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -4250,28 +5470,35 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>970</v>
+        <v>6657</v>
       </c>
       <c r="E5" t="n">
-        <v>4</v>
+        <v>6657</v>
       </c>
       <c r="F5" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="G5" t="n">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="H5" t="n">
-        <v>26</v>
+        <v>627</v>
       </c>
       <c r="I5" t="n">
-        <v>1540</v>
+        <v>3254</v>
       </c>
       <c r="J5" t="n">
-        <v>2900</v>
+        <v>23402</v>
       </c>
       <c r="K5" t="n">
-        <v>8183</v>
+        <v>46804</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>D
+복도
+2169</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -4289,28 +5516,35 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1170</v>
+        <v>54260</v>
       </c>
       <c r="E6" t="n">
-        <v>4</v>
+        <v>54260</v>
       </c>
       <c r="F6" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="G6" t="n">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="H6" t="n">
-        <v>26</v>
+        <v>627</v>
       </c>
       <c r="I6" t="n">
-        <v>1540</v>
+        <v>3254</v>
       </c>
       <c r="J6" t="n">
-        <v>2900</v>
+        <v>23402</v>
       </c>
       <c r="K6" t="n">
-        <v>8183</v>
+        <v>46804</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>D
+탈의실
+2145</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -4328,28 +5562,35 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>428</v>
       </c>
       <c r="E7" t="n">
-        <v>4</v>
+        <v>428</v>
       </c>
       <c r="F7" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="G7" t="n">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="H7" t="n">
-        <v>26</v>
+        <v>627</v>
       </c>
       <c r="I7" t="n">
-        <v>1540</v>
+        <v>3254</v>
       </c>
       <c r="J7" t="n">
-        <v>2900</v>
+        <v>23402</v>
       </c>
       <c r="K7" t="n">
-        <v>8183</v>
+        <v>46804</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>B
+PASS BOX(QHA-745)
+2142</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -4367,28 +5608,35 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>102</v>
       </c>
       <c r="E8" t="n">
-        <v>4</v>
+        <v>102</v>
       </c>
       <c r="F8" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="G8" t="n">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="H8" t="n">
-        <v>26</v>
+        <v>627</v>
       </c>
       <c r="I8" t="n">
-        <v>1540</v>
+        <v>3254</v>
       </c>
       <c r="J8" t="n">
-        <v>2900</v>
+        <v>23402</v>
       </c>
       <c r="K8" t="n">
-        <v>8183</v>
+        <v>46804</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>B
+PASS BOX(QHA-744)
+2142</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -4406,28 +5654,35 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2600</v>
+        <v>28320</v>
       </c>
       <c r="E9" t="n">
-        <v>4</v>
+        <v>28320</v>
       </c>
       <c r="F9" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="G9" t="n">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="H9" t="n">
-        <v>26</v>
+        <v>627</v>
       </c>
       <c r="I9" t="n">
-        <v>1540</v>
+        <v>3254</v>
       </c>
       <c r="J9" t="n">
-        <v>2900</v>
+        <v>23402</v>
       </c>
       <c r="K9" t="n">
-        <v>8183</v>
+        <v>46804</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>D
+PASS BOX(QHA-743)
+2169</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -4445,28 +5700,35 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="E10" t="n">
-        <v>4</v>
+        <v>65</v>
       </c>
       <c r="F10" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="G10" t="n">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="H10" t="n">
-        <v>26</v>
+        <v>627</v>
       </c>
       <c r="I10" t="n">
-        <v>1540</v>
+        <v>3254</v>
       </c>
       <c r="J10" t="n">
-        <v>2900</v>
+        <v>23402</v>
       </c>
       <c r="K10" t="n">
-        <v>8183</v>
+        <v>46804</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>D
+PASS BOX(QHA-742)
+2169</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -4484,28 +5746,35 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F11" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="G11" t="n">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="H11" t="n">
-        <v>26</v>
+        <v>627</v>
       </c>
       <c r="I11" t="n">
-        <v>1540</v>
+        <v>3254</v>
       </c>
       <c r="J11" t="n">
-        <v>2900</v>
+        <v>23402</v>
       </c>
       <c r="K11" t="n">
-        <v>8183</v>
+        <v>46804</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>A
+무균시험실 BSC
+2142</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -4523,28 +5792,32 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F12" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="G12" t="n">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="H12" t="n">
-        <v>26</v>
+        <v>627</v>
       </c>
       <c r="I12" t="n">
-        <v>1540</v>
+        <v>3254</v>
       </c>
       <c r="J12" t="n">
-        <v>2900</v>
+        <v>23402</v>
       </c>
       <c r="K12" t="n">
-        <v>8183</v>
+        <v>46804</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>B
+균주접종실 BSC
+2165</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -4562,28 +5835,35 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>418.3333333333333</v>
+        <v>4247</v>
       </c>
       <c r="E13" t="n">
-        <v>4</v>
+        <v>4247</v>
       </c>
       <c r="F13" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="G13" t="n">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="H13" t="n">
-        <v>26</v>
+        <v>627</v>
       </c>
       <c r="I13" t="n">
-        <v>1540</v>
+        <v>3254</v>
       </c>
       <c r="J13" t="n">
-        <v>2900</v>
+        <v>23402</v>
       </c>
       <c r="K13" t="n">
-        <v>8183</v>
+        <v>46804</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>C
+미생물 시험실
+2144</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -4604,25 +5884,32 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="G14" t="n">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="H14" t="n">
-        <v>26</v>
+        <v>627</v>
       </c>
       <c r="I14" t="n">
-        <v>1540</v>
+        <v>3254</v>
       </c>
       <c r="J14" t="n">
-        <v>2900</v>
+        <v>23402</v>
       </c>
       <c r="K14" t="n">
-        <v>8183</v>
+        <v>46804</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>B
+미생물 시험실 C/B(852)
+2144</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -4640,28 +5927,35 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>108</v>
       </c>
       <c r="E15" t="n">
-        <v>4</v>
+        <v>108</v>
       </c>
       <c r="F15" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="G15" t="n">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="H15" t="n">
-        <v>26</v>
+        <v>627</v>
       </c>
       <c r="I15" t="n">
-        <v>1540</v>
+        <v>3254</v>
       </c>
       <c r="J15" t="n">
-        <v>2900</v>
+        <v>23402</v>
       </c>
       <c r="K15" t="n">
-        <v>8183</v>
+        <v>46804</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>B
+미생물 시험실 C/B(853)
+2144</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -4679,28 +5973,35 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>7785</v>
+        <v>60755</v>
       </c>
       <c r="E16" t="n">
-        <v>4</v>
+        <v>60755</v>
       </c>
       <c r="F16" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="G16" t="n">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="H16" t="n">
-        <v>26</v>
+        <v>627</v>
       </c>
       <c r="I16" t="n">
-        <v>1540</v>
+        <v>3254</v>
       </c>
       <c r="J16" t="n">
-        <v>2900</v>
+        <v>23402</v>
       </c>
       <c r="K16" t="n">
-        <v>8183</v>
+        <v>46804</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>D
+착의실
+2146</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -4714,32 +6015,1140 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
+          <t>튜실</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>5070</v>
+      </c>
+      <c r="F17" t="n">
+        <v>23</v>
+      </c>
+      <c r="G17" t="n">
+        <v>46</v>
+      </c>
+      <c r="H17" t="n">
+        <v>627</v>
+      </c>
+      <c r="I17" t="n">
+        <v>3254</v>
+      </c>
+      <c r="J17" t="n">
+        <v>23402</v>
+      </c>
+      <c r="K17" t="n">
+        <v>46804</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>D
+튜실
+2150</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>2148</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>착의실</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>10285</v>
+      </c>
+      <c r="E18" t="n">
+        <v>10285</v>
+      </c>
+      <c r="F18" t="n">
+        <v>23</v>
+      </c>
+      <c r="G18" t="n">
+        <v>46</v>
+      </c>
+      <c r="H18" t="n">
+        <v>627</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3254</v>
+      </c>
+      <c r="J18" t="n">
+        <v>23402</v>
+      </c>
+      <c r="K18" t="n">
+        <v>46804</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>C
+착의실
+2148</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2149</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>착의실</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>374</v>
+      </c>
+      <c r="E19" t="n">
+        <v>374</v>
+      </c>
+      <c r="F19" t="n">
+        <v>23</v>
+      </c>
+      <c r="G19" t="n">
+        <v>46</v>
+      </c>
+      <c r="H19" t="n">
+        <v>627</v>
+      </c>
+      <c r="I19" t="n">
+        <v>3254</v>
+      </c>
+      <c r="J19" t="n">
+        <v>23402</v>
+      </c>
+      <c r="K19" t="n">
+        <v>46804</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>B
+착의실
+2149</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>2165</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>균주집중실</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>1990</v>
+      </c>
+      <c r="F20" t="n">
+        <v>23</v>
+      </c>
+      <c r="G20" t="n">
+        <v>46</v>
+      </c>
+      <c r="H20" t="n">
+        <v>627</v>
+      </c>
+      <c r="I20" t="n">
+        <v>3254</v>
+      </c>
+      <c r="J20" t="n">
+        <v>23402</v>
+      </c>
+      <c r="K20" t="n">
+        <v>46804</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>D
+균주집중실
+2165</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>2165</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>균주집중실 BSC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>2</v>
+      </c>
+      <c r="F21" t="n">
+        <v>23</v>
+      </c>
+      <c r="G21" t="n">
+        <v>46</v>
+      </c>
+      <c r="H21" t="n">
+        <v>627</v>
+      </c>
+      <c r="I21" t="n">
+        <v>3254</v>
+      </c>
+      <c r="J21" t="n">
+        <v>23402</v>
+      </c>
+      <c r="K21" t="n">
+        <v>46804</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>B
+균주집중실 BSC
+2165</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>2150</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
           <t>퇴실</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>5070</v>
+      </c>
+      <c r="F22" t="n">
+        <v>23</v>
+      </c>
+      <c r="G22" t="n">
+        <v>46</v>
+      </c>
+      <c r="H22" t="n">
+        <v>627</v>
+      </c>
+      <c r="I22" t="n">
+        <v>3254</v>
+      </c>
+      <c r="J22" t="n">
+        <v>23402</v>
+      </c>
+      <c r="K22" t="n">
+        <v>46804</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>D
+퇴실
+2150</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="45" customHeight="1">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>참고: 위 차트에서 특정 등급의 제한선이 표시되지 않는 경우, 해당 등급의 모든 측정 결과가 아직 기준을 만족하고 있음을 의미합니다. 해당 등급의 제한선은 제한값이 매우 높아 차트 표시 범위를 초과하므로 나타나지 않습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25"/>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A24:E25"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="28" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>청정등급</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>실번호</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>실명</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>2026 (상)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>2025 (하)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Grade A 경고기준: 4</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Grade A 조치기준: 8</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Grade B 경고기준: 13</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Grade B 조치기준: 26</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Grade C 경고기준: 1,540</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Grade C 조치기준: 2,900</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Grade D 경고기준: 8,183</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>표시명</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2142</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>무균 실험실</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>4.666666666666667</v>
+      </c>
+      <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G2" t="n">
+        <v>8</v>
+      </c>
+      <c r="H2" t="n">
+        <v>13</v>
+      </c>
+      <c r="I2" t="n">
+        <v>26</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1540</v>
+      </c>
+      <c r="K2" t="n">
+        <v>2900</v>
+      </c>
+      <c r="L2" t="n">
+        <v>8183</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>B
+무균 실험실
+2142</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2165</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>균주접종실</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>201.6666666666667</v>
+      </c>
+      <c r="F3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G3" t="n">
+        <v>8</v>
+      </c>
+      <c r="H3" t="n">
+        <v>13</v>
+      </c>
+      <c r="I3" t="n">
+        <v>26</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1540</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2900</v>
+      </c>
+      <c r="L3" t="n">
+        <v>8183</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>D
+균주접종실
+2165</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2147</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>탈의실</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>945</v>
+      </c>
+      <c r="E4" t="n">
+        <v>945</v>
+      </c>
+      <c r="F4" t="n">
+        <v>4</v>
+      </c>
+      <c r="G4" t="n">
+        <v>8</v>
+      </c>
+      <c r="H4" t="n">
+        <v>13</v>
+      </c>
+      <c r="I4" t="n">
+        <v>26</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1540</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2900</v>
+      </c>
+      <c r="L4" t="n">
+        <v>8183</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>C
+탈의실
+2147</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2169</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>복도</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>970</v>
+      </c>
+      <c r="E5" t="n">
+        <v>970</v>
+      </c>
+      <c r="F5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G5" t="n">
+        <v>8</v>
+      </c>
+      <c r="H5" t="n">
+        <v>13</v>
+      </c>
+      <c r="I5" t="n">
+        <v>26</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1540</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2900</v>
+      </c>
+      <c r="L5" t="n">
+        <v>8183</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>D
+복도
+2169</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2145</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>탈의실</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1170</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F6" t="n">
+        <v>4</v>
+      </c>
+      <c r="G6" t="n">
+        <v>8</v>
+      </c>
+      <c r="H6" t="n">
+        <v>13</v>
+      </c>
+      <c r="I6" t="n">
+        <v>26</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1540</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2900</v>
+      </c>
+      <c r="L6" t="n">
+        <v>8183</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>D
+탈의실
+2145</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2142</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>PASS BOX(QHA-745)</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" t="n">
+        <v>4</v>
+      </c>
+      <c r="G7" t="n">
+        <v>8</v>
+      </c>
+      <c r="H7" t="n">
+        <v>13</v>
+      </c>
+      <c r="I7" t="n">
+        <v>26</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1540</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2900</v>
+      </c>
+      <c r="L7" t="n">
+        <v>8183</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>B
+PASS BOX(QHA-745)
+2142</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2142</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>PASS BOX(QHA-744)</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>4</v>
+      </c>
+      <c r="G8" t="n">
+        <v>8</v>
+      </c>
+      <c r="H8" t="n">
+        <v>13</v>
+      </c>
+      <c r="I8" t="n">
+        <v>26</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1540</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2900</v>
+      </c>
+      <c r="L8" t="n">
+        <v>8183</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>B
+PASS BOX(QHA-744)
+2142</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2169</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>PASS BOX(QHA-743)</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>2600</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2600</v>
+      </c>
+      <c r="F9" t="n">
+        <v>4</v>
+      </c>
+      <c r="G9" t="n">
+        <v>8</v>
+      </c>
+      <c r="H9" t="n">
+        <v>13</v>
+      </c>
+      <c r="I9" t="n">
+        <v>26</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1540</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2900</v>
+      </c>
+      <c r="L9" t="n">
+        <v>8183</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>D
+PASS BOX(QHA-743)
+2169</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2169</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>PASS BOX(QHA-742)</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>4</v>
+      </c>
+      <c r="G10" t="n">
+        <v>8</v>
+      </c>
+      <c r="H10" t="n">
+        <v>13</v>
+      </c>
+      <c r="I10" t="n">
+        <v>26</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1540</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2900</v>
+      </c>
+      <c r="L10" t="n">
+        <v>8183</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>D
+PASS BOX(QHA-742)
+2169</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2142</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>무균시험실 BSC</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>4</v>
+      </c>
+      <c r="G11" t="n">
+        <v>8</v>
+      </c>
+      <c r="H11" t="n">
+        <v>13</v>
+      </c>
+      <c r="I11" t="n">
+        <v>26</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1540</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2900</v>
+      </c>
+      <c r="L11" t="n">
+        <v>8183</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>A
+무균시험실 BSC
+2142</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2165</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>균주접종실 BSC</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>4</v>
+      </c>
+      <c r="G12" t="n">
+        <v>8</v>
+      </c>
+      <c r="H12" t="n">
+        <v>13</v>
+      </c>
+      <c r="I12" t="n">
+        <v>26</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1540</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2900</v>
+      </c>
+      <c r="L12" t="n">
+        <v>8183</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>B
+균주접종실 BSC
+2165</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2144</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>미생물 시험실</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>418.3333333333333</v>
+      </c>
+      <c r="E13" t="n">
+        <v>418.3333333333333</v>
+      </c>
+      <c r="F13" t="n">
+        <v>4</v>
+      </c>
+      <c r="G13" t="n">
+        <v>8</v>
+      </c>
+      <c r="H13" t="n">
+        <v>13</v>
+      </c>
+      <c r="I13" t="n">
+        <v>26</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1540</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2900</v>
+      </c>
+      <c r="L13" t="n">
+        <v>8183</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>C
+미생물 시험실
+2144</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2144</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>미생물 시험실 C/B(852)</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>4</v>
+      </c>
+      <c r="G14" t="n">
+        <v>8</v>
+      </c>
+      <c r="H14" t="n">
+        <v>13</v>
+      </c>
+      <c r="I14" t="n">
+        <v>26</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1540</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2900</v>
+      </c>
+      <c r="L14" t="n">
+        <v>8183</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>B
+미생물 시험실 C/B(852)
+2144</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2144</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>미생물 시험실 C/B(853)</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" t="n">
+        <v>4</v>
+      </c>
+      <c r="G15" t="n">
+        <v>8</v>
+      </c>
+      <c r="H15" t="n">
+        <v>13</v>
+      </c>
+      <c r="I15" t="n">
+        <v>26</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1540</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2900</v>
+      </c>
+      <c r="L15" t="n">
+        <v>8183</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>B
+미생물 시험실 C/B(853)
+2144</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2146</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>착의실</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>7785</v>
+      </c>
+      <c r="E16" t="n">
+        <v>7785</v>
+      </c>
+      <c r="F16" t="n">
+        <v>4</v>
+      </c>
+      <c r="G16" t="n">
+        <v>8</v>
+      </c>
+      <c r="H16" t="n">
+        <v>13</v>
+      </c>
+      <c r="I16" t="n">
+        <v>26</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1540</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2900</v>
+      </c>
+      <c r="L16" t="n">
+        <v>8183</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>D
+착의실
+2146</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2150</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>튜실</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>230</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" t="n">
         <v>4</v>
       </c>
-      <c r="F17" t="n">
+      <c r="G17" t="n">
         <v>8</v>
       </c>
-      <c r="G17" t="n">
+      <c r="H17" t="n">
         <v>13</v>
       </c>
-      <c r="H17" t="n">
+      <c r="I17" t="n">
         <v>26</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>1540</v>
       </c>
-      <c r="J17" t="n">
+      <c r="K17" t="n">
         <v>2900</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>8183</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>D
+튜실
+2150</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -4760,25 +7169,35 @@
         <v>560</v>
       </c>
       <c r="E18" t="n">
+        <v>560</v>
+      </c>
+      <c r="F18" t="n">
         <v>4</v>
       </c>
-      <c r="F18" t="n">
+      <c r="G18" t="n">
         <v>8</v>
       </c>
-      <c r="G18" t="n">
+      <c r="H18" t="n">
         <v>13</v>
       </c>
-      <c r="H18" t="n">
+      <c r="I18" t="n">
         <v>26</v>
       </c>
-      <c r="I18" t="n">
+      <c r="J18" t="n">
         <v>1540</v>
       </c>
-      <c r="J18" t="n">
+      <c r="K18" t="n">
         <v>2900</v>
       </c>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
         <v>8183</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>C
+착의실
+2148</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -4802,35 +7221,183 @@
         <v>4</v>
       </c>
       <c r="F19" t="n">
+        <v>4</v>
+      </c>
+      <c r="G19" t="n">
         <v>8</v>
       </c>
-      <c r="G19" t="n">
+      <c r="H19" t="n">
         <v>13</v>
       </c>
-      <c r="H19" t="n">
+      <c r="I19" t="n">
         <v>26</v>
       </c>
-      <c r="I19" t="n">
+      <c r="J19" t="n">
         <v>1540</v>
       </c>
-      <c r="J19" t="n">
+      <c r="K19" t="n">
         <v>2900</v>
       </c>
-      <c r="K19" t="n">
+      <c r="L19" t="n">
         <v>8183</v>
       </c>
-    </row>
-    <row r="21" ht="45" customHeight="1">
-      <c r="A21" s="9" t="inlineStr">
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>B
+착의실
+2149</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>2165</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>균주집중실</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>201.6666666666667</v>
+      </c>
+      <c r="F20" t="n">
+        <v>4</v>
+      </c>
+      <c r="G20" t="n">
+        <v>8</v>
+      </c>
+      <c r="H20" t="n">
+        <v>13</v>
+      </c>
+      <c r="I20" t="n">
+        <v>26</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1540</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2900</v>
+      </c>
+      <c r="L20" t="n">
+        <v>8183</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>D
+균주집중실
+2165</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>2165</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>균주집중실 BSC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>4</v>
+      </c>
+      <c r="G21" t="n">
+        <v>8</v>
+      </c>
+      <c r="H21" t="n">
+        <v>13</v>
+      </c>
+      <c r="I21" t="n">
+        <v>26</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1540</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2900</v>
+      </c>
+      <c r="L21" t="n">
+        <v>8183</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>B
+균주집중실 BSC
+2165</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>2150</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>퇴실</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>230</v>
+      </c>
+      <c r="F22" t="n">
+        <v>4</v>
+      </c>
+      <c r="G22" t="n">
+        <v>8</v>
+      </c>
+      <c r="H22" t="n">
+        <v>13</v>
+      </c>
+      <c r="I22" t="n">
+        <v>26</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1540</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2900</v>
+      </c>
+      <c r="L22" t="n">
+        <v>8183</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>D
+퇴실
+2150</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="45" customHeight="1">
+      <c r="A24" s="9" t="inlineStr">
         <is>
           <t>참고: 위 차트에서 특정 등급의 제한선이 표시되지 않는 경우, 해당 등급의 모든 측정 결과가 아직 기준을 만족하고 있음을 의미합니다. 해당 등급의 제한선은 제한값이 매우 높아 차트 표시 범위를 초과하므로 나타나지 않습니다.</t>
         </is>
       </c>
     </row>
-    <row r="22"/>
+    <row r="25"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A21:D22"/>
+    <mergeCell ref="A24:E25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
